--- a/data/excel/admissions_registry.xlsx
+++ b/data/excel/admissions_registry.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="5340" yWindow="2316" windowWidth="17280" windowHeight="9420" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Applicants" sheetId="1" state="visible" r:id="rId1"/>
@@ -11,7 +12,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Applicants'!$A$1:$V$2</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -52,7 +53,7 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -416,18 +417,18 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:V2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="60" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
@@ -435,7 +436,7 @@
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="35" customWidth="1" min="17" max="17"/>
-    <col width="27" customWidth="1" min="18" max="18"/>
+    <col width="53" customWidth="1" min="18" max="18"/>
     <col width="18" customWidth="1" min="19" max="19"/>
     <col width="23" customWidth="1" min="20" max="20"/>
     <col width="26" customWidth="1" min="21" max="21"/>
@@ -556,87 +557,91 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7939104831</v>
+        <v>5394280567</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>kotakbaser</t>
+          <t>spisoq</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://t.me/kotakbaser</t>
+          <t>https://t.me/spisoq</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>алалла</t>
+          <t>grgrgrg</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+77382873728</t>
+          <t>+77004287470</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Студент</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Инженерные технологии</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6B11380 - Вычислительная техника и программное обеспечение</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ВТПО 23-1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Telegram file_id: AgACAgQAAxkBAAIE7GnrUb_a-6Wp9etMHyL8ZQS54dk-AALwC2sbXwNZU5dexFTzM8eSAQADAgADeAADOwQ</t>
+          <t>Telegram file_id: AgACAgIAAxkBAAIJ6WoKH4mHrHW6Md7lvGUkJl6HKDptAAL7HmsbN2ZQSLPiMeUW-uXHAQADAgADeQADOwQ; server_path: data/files/5394280567/attestat_diplom.jpg</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Telegram file_id: AgACAgQAAxkBAAIE7GnrUb_a-6Wp9etMHyL8ZQS54dk-AALwC2sbXwNZU5dexFTzM8eSAQADAgADeAADOwQ</t>
+          <t>Telegram file_id: AgACAgIAAxkBAAIJ6WoKH4mHrHW6Md7lvGUkJl6HKDptAAL7HmsbN2ZQSLPiMeUW-uXHAQADAgADeQADOwQ; server_path: data/files/5394280567/udostoverenie.jpg</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Telegram file_id: AgACAgQAAxkBAAIE7GnrUb_a-6Wp9etMHyL8ZQS54dk-AALwC2sbXwNZU5dexFTzM8eSAQADAgADeAADOwQ</t>
+          <t>Telegram file_id: AgACAgIAAxkBAAIJ6WoKH4mHrHW6Md7lvGUkJl6HKDptAAL7HmsbN2ZQSLPiMeUW-uXHAQADAgADeQADOwQ; server_path: data/files/5394280567/photo_3x4.jpg</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Telegram file_id: AgACAgQAAxkBAAIE7GnrUb_a-6Wp9etMHyL8ZQS54dk-AALwC2sbXwNZU5dexFTzM8eSAQADAgADeAADOwQ</t>
+          <t>Telegram file_id: AgACAgIAAxkBAAIJ6WoKH4mHrHW6Md7lvGUkJl6HKDptAAL7HmsbN2ZQSLPiMeUW-uXHAQADAgADeQADOwQ; server_path: data/files/5394280567/med_075u.jpg</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Telegram file_id: AgACAgQAAxkBAAIE7GnrUb_a-6Wp9etMHyL8ZQS54dk-AALwC2sbXwNZU5dexFTzM8eSAQADAgADeAADOwQ</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr"/>
+          <t>Telegram file_id: AgACAgIAAxkBAAIJ6WoKH4mHrHW6Md7lvGUkJl6HKDptAAL7HmsbN2ZQSLPiMeUW-uXHAQADAgADeQADOwQ; server_path: data/files/5394280567/ent_certificate.jpg</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>efef</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Педагогика</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6В01301 - Педагогика и методика начального обучения</t>
         </is>
       </c>
       <c r="S2" s="1" t="inlineStr">
@@ -644,8 +649,12 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="T2" s="1" t="inlineStr"/>
-      <c r="U2" s="1" t="inlineStr"/>
+      <c r="T2" s="1" t="n">
+        <v>450000</v>
+      </c>
+      <c r="U2" s="1" t="n">
+        <v>1800000</v>
+      </c>
       <c r="V2" t="inlineStr">
         <is>
           <t>approved</t>
